--- a/ksoft/docs/stock/Bestand_Decorative Paper_Set up_details.XLSX
+++ b/ksoft/docs/stock/Bestand_Decorative Paper_Set up_details.XLSX
@@ -9072,13 +9072,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60DDC7C0-B34F-41BC-8D4D-06CEBFF6D4EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1C2C348-3939-43A4-95B0-2B3A01BD89A5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89A14C9F-4C39-4E0A-82CC-3558EFDBCE97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4292FE0B-C91E-45EA-A077-B5F286FBC961}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4CE3197-0C8D-4991-BEE0-44540D0C9663}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54DE7279-5095-4632-8B2D-392D6CA292BC}"/>
 </file>
--- a/ksoft/docs/stock/Bestand_Decorative Paper_Set up_details.XLSX
+++ b/ksoft/docs/stock/Bestand_Decorative Paper_Set up_details.XLSX
@@ -9072,13 +9072,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1C2C348-3939-43A4-95B0-2B3A01BD89A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60DDC7C0-B34F-41BC-8D4D-06CEBFF6D4EA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4292FE0B-C91E-45EA-A077-B5F286FBC961}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89A14C9F-4C39-4E0A-82CC-3558EFDBCE97}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54DE7279-5095-4632-8B2D-392D6CA292BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4CE3197-0C8D-4991-BEE0-44540D0C9663}"/>
 </file>